--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Service of Papers with Subp Ã¦ n</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 35</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 7</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 35</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -669,7 +677,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 36â€”37</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 35</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -724,14 +732,14 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 36â€”37</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: 86—87 •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: 34</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -779,14 +787,14 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 86â€”87 â€¢</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L20: isolated marker/symbol line :: 34</t>
+          <t>L19: isolated marker/symbol line :: 34</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -830,14 +838,14 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L21: isolated marker/symbol line :: 34</t>
+          <t>L20: isolated marker/symbol line :: 34</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -881,14 +889,14 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: 34</t>
+          <t>L21: isolated marker/symbol line :: 34</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -932,14 +940,14 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: May be read against an Answer.•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: 35</t>
+          <t>L22: isolated marker/symbol line :: 34</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -983,19 +991,19 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: May be read against an Answer.â€¢</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 1</t>
+          <t>L23: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L58: symbol-only separator/garbage line :: . 35</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 35</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1022,7 +1030,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1034,19 +1042,19 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: 35</t>
+          <t>L24: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 35</t>
+          <t>L58: symbol-only separator/garbage line :: . 35</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1073,7 +1081,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1085,19 +1093,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 35</t>
+          <t>L25: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L62: symbol-only separator/garbage line :: .36</t>
+          <t>L60: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1119,12 +1127,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1134,21 +1142,17 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: 35</t>
+          <t>L27: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 113</t>
+          <t>L62: symbol-only separator/garbage line :: .36</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1190,12 +1194,12 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 36</t>
+          <t>L28: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 113</t>
+          <t>L63: symbol-only separator/garbage line :: 36—37</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1222,7 +1226,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1237,12 +1241,12 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L31: symbol-only separator/garbage line :: 36-37</t>
+          <t>L29: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 139</t>
+          <t>L65: symbol-only separator/garbage line :: . 36—37</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1284,12 +1288,12 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 1</t>
+          <t>L31: symbol-only separator/garbage line :: 36-37</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 154</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: 86—87 •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1331,12 +1335,12 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L44: symbol-only separator/garbage line :: 36-37</t>
+          <t>L43: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 85</t>
+          <t>L69: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1378,12 +1382,12 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L46: symbol-only separator/garbage line :: 86-87</t>
+          <t>L44: symbol-only separator/garbage line :: 36-37</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 85</t>
+          <t>L71: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1413,12 +1417,12 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 113</t>
+          <t>L46: symbol-only separator/garbage line :: 86-87</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 105</t>
+          <t>L73: isolated marker/symbol line :: 139</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1448,12 +1452,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 113</t>
+          <t>L47: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L75: isolated marker/symbol line :: 154</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1483,12 +1487,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 139</t>
+          <t>L49: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1518,12 +1522,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 154</t>
+          <t>L51: isolated marker/symbol line :: 139</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L79: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1553,12 +1557,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 85</t>
+          <t>L52: isolated marker/symbol line :: 154</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L81: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1588,12 +1592,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 85</t>
+          <t>L54: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1623,12 +1627,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 105</t>
+          <t>L55: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1642,6 +1646,134 @@
       <c r="X24" s="1" t="inlineStr"/>
       <c r="Y24" s="1" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr"/>
+      <c r="D25" s="1" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
+      <c r="F25" s="1" t="inlineStr"/>
+      <c r="G25" s="1" t="inlineStr"/>
+      <c r="H25" s="1" t="inlineStr"/>
+      <c r="I25" s="1" t="inlineStr"/>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
+      <c r="L25" s="1" t="inlineStr"/>
+      <c r="M25" s="1" t="inlineStr"/>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t>L57: isolated marker/symbol line :: 105</t>
+        </is>
+      </c>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P25" s="1" t="inlineStr"/>
+      <c r="Q25" s="1" t="inlineStr"/>
+      <c r="R25" s="1" t="inlineStr"/>
+      <c r="S25" s="1" t="inlineStr"/>
+      <c r="T25" s="1" t="inlineStr"/>
+      <c r="U25" s="1" t="inlineStr"/>
+      <c r="V25" s="1" t="inlineStr"/>
+      <c r="W25" s="1" t="inlineStr"/>
+      <c r="X25" s="1" t="inlineStr"/>
+      <c r="Y25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr"/>
+      <c r="D26" s="1" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
+      <c r="F26" s="1" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr"/>
+      <c r="H26" s="1" t="inlineStr"/>
+      <c r="I26" s="1" t="inlineStr"/>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
+      <c r="L26" s="1" t="inlineStr"/>
+      <c r="M26" s="1" t="inlineStr"/>
+      <c r="N26" s="1" t="inlineStr"/>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P26" s="1" t="inlineStr"/>
+      <c r="Q26" s="1" t="inlineStr"/>
+      <c r="R26" s="1" t="inlineStr"/>
+      <c r="S26" s="1" t="inlineStr"/>
+      <c r="T26" s="1" t="inlineStr"/>
+      <c r="U26" s="1" t="inlineStr"/>
+      <c r="V26" s="1" t="inlineStr"/>
+      <c r="W26" s="1" t="inlineStr"/>
+      <c r="X26" s="1" t="inlineStr"/>
+      <c r="Y26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr"/>
+      <c r="D27" s="1" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr"/>
+      <c r="F27" s="1" t="inlineStr"/>
+      <c r="G27" s="1" t="inlineStr"/>
+      <c r="H27" s="1" t="inlineStr"/>
+      <c r="I27" s="1" t="inlineStr"/>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
+      <c r="L27" s="1" t="inlineStr"/>
+      <c r="M27" s="1" t="inlineStr"/>
+      <c r="N27" s="1" t="inlineStr"/>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P27" s="1" t="inlineStr"/>
+      <c r="Q27" s="1" t="inlineStr"/>
+      <c r="R27" s="1" t="inlineStr"/>
+      <c r="S27" s="1" t="inlineStr"/>
+      <c r="T27" s="1" t="inlineStr"/>
+      <c r="U27" s="1" t="inlineStr"/>
+      <c r="V27" s="1" t="inlineStr"/>
+      <c r="W27" s="1" t="inlineStr"/>
+      <c r="X27" s="1" t="inlineStr"/>
+      <c r="Y27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr"/>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr"/>
+      <c r="G28" s="1" t="inlineStr"/>
+      <c r="H28" s="1" t="inlineStr"/>
+      <c r="I28" s="1" t="inlineStr"/>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
+      <c r="L28" s="1" t="inlineStr"/>
+      <c r="M28" s="1" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr"/>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="inlineStr"/>
+      <c r="R28" s="1" t="inlineStr"/>
+      <c r="S28" s="1" t="inlineStr"/>
+      <c r="T28" s="1" t="inlineStr"/>
+      <c r="U28" s="1" t="inlineStr"/>
+      <c r="V28" s="1" t="inlineStr"/>
+      <c r="W28" s="1" t="inlineStr"/>
+      <c r="X28" s="1" t="inlineStr"/>
+      <c r="Y28" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
